--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92552474168</v>
+        <v>46157.93105479411</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105479411</v>
+        <v>46157.93131182162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131182162</v>
+        <v>46157.93379247664</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93379247664</v>
+        <v>46157.93689501937</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93689501937</v>
+        <v>46158.2820269547</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820269547</v>
+        <v>46158.29732567175</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29732567175</v>
+        <v>46158.29801909288</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29801909288</v>
+        <v>46158.3336624415</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3336624415</v>
+        <v>46158.37218013764</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218013764</v>
+        <v>46158.37273278874</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
